--- a/output/2026-09-16_01_Croazia_Brodsko-posavska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-16_01_Croazia_Brodsko-posavska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore di macchine e attrezzature industriali/edili, utensili per metallo; vendita, noleggio e assistenza. Attiva dal 1995. Confermata su fininfo.hr, tvrtke.hr, sito ufficiale.</t>
+          <t>Distributore di macchine e attrezzature industriali/edili, utensili per metallo; vendita, noleggio e assistenza. Attiva dal 1995. Confermata su fininfo.hr, tvrtke.hr, sito ufficiale. [DUPLICATO — vedi anche: 2026-09-15_20_Croazia_Brodsko-posavska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Distributore/rivenditore di utensili elettrici, a batteria e a scoppio (Makita, Metabo, Bosch, Dewalt, Ruko) e produttore proprio di DPI/abbigliamento da lavoro. Attiva dal 1991. Nota: alcune fonti riportano indirizzo Mirka Iličića 2 anziché Eugena Kumičića 57 (probabile doppia sede/aggiornamento indirizzo).</t>
+          <t>Distributore/rivenditore di utensili elettrici, a batteria e a scoppio (Makita, Metabo, Bosch, Dewalt, Ruko) e produttore proprio di DPI/abbigliamento da lavoro. Attiva dal 1991. Nota: alcune fonti riportano indirizzo Mirka Iličića 2 anziché Eugena Kumičića 57 (probabile doppia sede/aggiornamento indirizzo). [DUPLICATO — vedi anche: 2026-09-15_21_Croazia_Brodsko-posavska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rivenditore con reparto utensili (manuali, elettrici, pneumatici) all'interno di un assortimento più ampio (elettromateriale, ferramenta, elettrodomestici, materiali edili minori). Attiva dal 1990. Nota: attività commerciale mista, non esclusivamente utensili/macchine utensili.</t>
+          <t>Rivenditore con reparto utensili (manuali, elettrici, pneumatici) all'interno di un assortimento più ampio (elettromateriale, ferramenta, elettrodomestici, materiali edili minori). Attiva dal 1990. Nota: attività commerciale mista, non esclusivamente utensili/macchine utensili. [DUPLICATO — vedi anche: 2026-09-15_23_Croazia_Brodsko-posavska_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">

--- a/output/2026-09-16_01_Croazia_Brodsko-posavska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-16_01_Croazia_Brodsko-posavska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
